--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487790_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487790_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.0803</v>
+        <v>5.1099</v>
       </c>
       <c r="E2" t="n">
-        <v>2.1228</v>
+        <v>3.1525</v>
       </c>
       <c r="F2" t="n">
         <v>1.9575</v>
@@ -610,10 +610,10 @@
         <v>2.2893</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.1711</v>
+        <v>-0.1414</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.0191</v>
+        <v>0.0105</v>
       </c>
       <c r="U2" t="n">
         <v>-0.152</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0885</v>
+        <v>0.5157</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.4655</v>
+        <v>-0.7154</v>
       </c>
       <c r="F3" t="n">
-        <v>1.554</v>
+        <v>1.2311</v>
       </c>
       <c r="G3" t="n">
         <v>-0.2283</v>
@@ -688,13 +688,13 @@
         <v>1.6649</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0567</v>
+        <v>0.3704</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5624</v>
+        <v>0.1877</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5057</v>
+        <v>0.1827</v>
       </c>
       <c r="V3" t="n">
         <v>-1.2914</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. MARTINEZ MEGIAS</t>
+          <t>A. CAÑETE PUENTENUEVA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.3745</v>
+        <v>-0.344</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.6422</v>
+        <v>-0.0414</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2677</v>
+        <v>-0.3026</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.9833</v>
+        <v>-0.7478</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.5677</v>
+        <v>0.3519</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4155</v>
+        <v>-1.0997</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.1422</v>
+        <v>0.1543</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.2205</v>
+        <v>0.1151</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0784</v>
+        <v>0.0392</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.8411</v>
+        <v>-0.9022</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3472</v>
+        <v>0.2367</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.4939</v>
+        <v>-1.1389</v>
       </c>
       <c r="P4" t="n">
         <v>0.4162</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.4974</v>
+        <v>0.4162</v>
       </c>
       <c r="S4" t="n">
-        <v>1.6701</v>
+        <v>-0.0124</v>
       </c>
       <c r="T4" t="n">
-        <v>1.0588</v>
+        <v>-0.1957</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6114000000000001</v>
+        <v>0.1833</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.4776</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.4776</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. CAÑETE PUENTENUEVA</t>
+          <t>J. BALDERAS MARTÍN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.4092</v>
+        <v>-0.3538</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1067</v>
+        <v>-1.1779</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3026</v>
+        <v>0.8241000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.7478</v>
+        <v>-0.3825</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3519</v>
+        <v>0.2559</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.0997</v>
+        <v>-0.6384</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1543</v>
+        <v>-0.656</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1151</v>
+        <v>0.0192</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0392</v>
+        <v>-0.6752</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.9022</v>
+        <v>0.2735</v>
       </c>
       <c r="N5" t="n">
         <v>0.2367</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.1389</v>
+        <v>0.0367</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4162</v>
+        <v>0.8325</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4162</v>
+        <v>0.8325</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0776</v>
+        <v>-0.8038</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.261</v>
+        <v>-0.5219</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1833</v>
+        <v>-0.2818</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. BALDERAS MARTÍN</t>
+          <t>L. FAIAL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4419</v>
+        <v>-0.9298</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.1779</v>
+        <v>0.1725</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7361</v>
+        <v>-1.1023</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.3825</v>
+        <v>-1.4249</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2559</v>
+        <v>0.3174</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6384</v>
+        <v>-1.7423</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.656</v>
+        <v>-0.796</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0192</v>
+        <v>1.5218</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6752</v>
+        <v>-2.3178</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2735</v>
+        <v>-0.6289</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2367</v>
+        <v>-1.2044</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0367</v>
+        <v>0.5756</v>
       </c>
       <c r="P6" t="n">
-        <v>0.8325</v>
+        <v>1.0406</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.8325</v>
+        <v>1.0406</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8919</v>
+        <v>-0.6694</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5219</v>
+        <v>-0.199</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3699</v>
+        <v>-0.4703</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.1238</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.1675</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.0437</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. FAIAL</t>
+          <t>J. MARTINEZ MEGIAS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9363</v>
+        <v>-1.4895</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1072</v>
+        <v>-3.4342</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.0436</v>
+        <v>1.9447</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.4249</v>
+        <v>-1.9833</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3174</v>
+        <v>-1.5677</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.7423</v>
+        <v>-0.4155</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.796</v>
+        <v>-1.1422</v>
       </c>
       <c r="K7" t="n">
-        <v>1.5218</v>
+        <v>-1.2205</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.3178</v>
+        <v>0.0784</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.6289</v>
+        <v>-0.8411</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.2044</v>
+        <v>-0.3472</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5756</v>
+        <v>-0.4939</v>
       </c>
       <c r="P7" t="n">
-        <v>1.0406</v>
+        <v>0.4162</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-2.0812</v>
       </c>
       <c r="R7" t="n">
-        <v>1.0406</v>
+        <v>2.4974</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6758999999999999</v>
+        <v>0.5552</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2643</v>
+        <v>0.2668</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4116</v>
+        <v>0.2884</v>
       </c>
       <c r="V7" t="n">
-        <v>0.1238</v>
+        <v>-0.4776</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1675</v>
+        <v>-0.4776</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0437</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.7216</v>
+        <v>-2.0915</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7306</v>
+        <v>-1.1592</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.991</v>
+        <v>-0.9323</v>
       </c>
       <c r="G8" t="n">
         <v>0.01</v>
@@ -1078,13 +1078,13 @@
         <v>1.4568</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.06660000000000001</v>
+        <v>-0.4365</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6054</v>
+        <v>0.1767</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6719000000000001</v>
+        <v>-0.6132</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.7563</v>
+        <v>-3.8429</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.675</v>
+        <v>-2.9965</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.0812</v>
+        <v>-0.8464</v>
       </c>
       <c r="G9" t="n">
         <v>-3.0653</v>
@@ -1156,13 +1156,13 @@
         <v>1.0406</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.794</v>
+        <v>-0.8806</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.199</v>
+        <v>-0.5205</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.595</v>
+        <v>-0.3601</v>
       </c>
       <c r="V9" t="n">
         <v>-0.9376</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.1742</v>
+        <v>-4.6638</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.3622</v>
+        <v>-2.9399</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.812</v>
+        <v>-1.7239</v>
       </c>
       <c r="G10" t="n">
         <v>-1.9808</v>
@@ -1234,13 +1234,13 @@
         <v>1.2487</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3204</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4501</v>
+        <v>-0.1276</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7705</v>
+        <v>-0.6824</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>F. LOPEZ JIMENEZ</t>
+          <t>J. SANTA BARBARA CARCELEN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.8026</v>
+        <v>-4.8578</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.3611</v>
+        <v>-2.03</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.4415</v>
+        <v>-2.8278</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.3907</v>
+        <v>-1.8096</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.9318</v>
+        <v>-0.7719</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.4589</v>
+        <v>-1.0377</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.3578</v>
+        <v>-1.1971</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.9681999999999999</v>
+        <v>-0.4737</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.3896</v>
+        <v>-0.7234</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.0329</v>
+        <v>-0.6125</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.9636</v>
+        <v>-0.2982</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.0694</v>
+        <v>-0.3143</v>
       </c>
       <c r="P11" t="n">
-        <v>0.8325</v>
+        <v>0.2081</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R11" t="n">
-        <v>0.8325</v>
+        <v>1.2487</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0907</v>
+        <v>-0.6912</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0033</v>
+        <v>0.2077</v>
       </c>
       <c r="U11" t="n">
-        <v>0.094</v>
+        <v>-0.899</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.3351</v>
+        <v>-2.565</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.3351</v>
+        <v>-2.565</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. SANTA BARBARA CARCELEN</t>
+          <t>F. LOPEZ JIMENEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.9117</v>
+        <v>-5.086</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.6729</v>
+        <v>-2.4682</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.2388</v>
+        <v>-2.6177</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.8096</v>
+        <v>-3.3907</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.7719</v>
+        <v>-1.9318</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.0377</v>
+        <v>-1.4589</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.1971</v>
+        <v>-2.3578</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.4737</v>
+        <v>-0.9681999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.7234</v>
+        <v>-1.3896</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.6125</v>
+        <v>-1.0329</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.2982</v>
+        <v>-0.9636</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.3143</v>
+        <v>-0.0694</v>
       </c>
       <c r="P12" t="n">
-        <v>0.2081</v>
+        <v>0.8325</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2487</v>
+        <v>0.8325</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.7452</v>
+        <v>-0.1926</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4352</v>
+        <v>-0.1105</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.31</v>
+        <v>-0.0822</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.565</v>
+        <v>-2.3351</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.565</v>
+        <v>-2.3351</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-18.3595</v>
+        <v>-18.0335</v>
       </c>
       <c r="E13" t="n">
-        <v>-13.9641</v>
+        <v>-13.6377</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.3954</v>
+        <v>-4.3956</v>
       </c>
       <c r="G13" t="n">
         <v>-11.0005</v>
@@ -1438,7 +1438,7 @@
         <v>-4.2447</v>
       </c>
       <c r="I13" t="n">
-        <v>-6.7557</v>
+        <v>-6.755699999999999</v>
       </c>
       <c r="J13" t="n">
         <v>-3.2023</v>
@@ -1468,13 +1468,13 @@
         <v>14.5682</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.038600000000001</v>
+        <v>-3.712299999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.1519</v>
+        <v>-0.8258000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.8865</v>
+        <v>-2.8866</v>
       </c>
       <c r="V13" t="n">
         <v>-7.482900000000001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.3527</v>
+        <v>6.4305</v>
       </c>
       <c r="E14" t="n">
-        <v>4.3985</v>
+        <v>4.5057</v>
       </c>
       <c r="F14" t="n">
-        <v>1.9542</v>
+        <v>1.9248</v>
       </c>
       <c r="G14" t="n">
         <v>3.8908</v>
@@ -1546,13 +1546,13 @@
         <v>0.8325</v>
       </c>
       <c r="S14" t="n">
-        <v>1.5025</v>
+        <v>1.5803</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2948</v>
+        <v>0.402</v>
       </c>
       <c r="U14" t="n">
-        <v>1.2077</v>
+        <v>1.1783</v>
       </c>
       <c r="V14" t="n">
         <v>1.1675</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. STRIKKER</t>
+          <t>A. MAZAIRA GOMEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.4978</v>
+        <v>6.159</v>
       </c>
       <c r="E15" t="n">
-        <v>2.2492</v>
+        <v>2.3532</v>
       </c>
       <c r="F15" t="n">
-        <v>3.2485</v>
+        <v>3.8058</v>
       </c>
       <c r="G15" t="n">
-        <v>4.0026</v>
+        <v>2.9391</v>
       </c>
       <c r="H15" t="n">
-        <v>2.6612</v>
+        <v>1.2026</v>
       </c>
       <c r="I15" t="n">
-        <v>1.3414</v>
+        <v>1.7365</v>
       </c>
       <c r="J15" t="n">
-        <v>2.0883</v>
+        <v>1.4658</v>
       </c>
       <c r="K15" t="n">
-        <v>2.1063</v>
+        <v>0.6967</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.018</v>
+        <v>0.769</v>
       </c>
       <c r="M15" t="n">
-        <v>1.9143</v>
+        <v>1.4734</v>
       </c>
       <c r="N15" t="n">
-        <v>0.5548999999999999</v>
+        <v>0.5059</v>
       </c>
       <c r="O15" t="n">
-        <v>1.3594</v>
+        <v>0.9675</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.6244</v>
+        <v>1.0406</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.0812</v>
+        <v>-1.0406</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4568</v>
+        <v>2.0812</v>
       </c>
       <c r="S15" t="n">
-        <v>1.5358</v>
+        <v>0.428</v>
       </c>
       <c r="T15" t="n">
-        <v>1.6583</v>
+        <v>0.1767</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1226</v>
+        <v>0.2513</v>
       </c>
       <c r="V15" t="n">
-        <v>0.5838</v>
+        <v>1.7513</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5838</v>
+        <v>1.7513</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. MAZAIRA GOMEZ</t>
+          <t>M. STRIKKER</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.2215</v>
+        <v>5.189</v>
       </c>
       <c r="E16" t="n">
-        <v>1.496</v>
+        <v>1.7135</v>
       </c>
       <c r="F16" t="n">
-        <v>3.7256</v>
+        <v>3.4756</v>
       </c>
       <c r="G16" t="n">
-        <v>2.9391</v>
+        <v>4.0026</v>
       </c>
       <c r="H16" t="n">
-        <v>1.2026</v>
+        <v>2.6612</v>
       </c>
       <c r="I16" t="n">
-        <v>1.7365</v>
+        <v>1.3414</v>
       </c>
       <c r="J16" t="n">
-        <v>1.4658</v>
+        <v>2.0883</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6967</v>
+        <v>2.1063</v>
       </c>
       <c r="L16" t="n">
-        <v>0.769</v>
+        <v>-0.018</v>
       </c>
       <c r="M16" t="n">
-        <v>1.4734</v>
+        <v>1.9143</v>
       </c>
       <c r="N16" t="n">
-        <v>0.5059</v>
+        <v>0.5548999999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>0.9675</v>
+        <v>1.3594</v>
       </c>
       <c r="P16" t="n">
-        <v>1.0406</v>
+        <v>-0.6244</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R16" t="n">
-        <v>2.0812</v>
+        <v>1.4568</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5095</v>
+        <v>1.227</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6805</v>
+        <v>1.1226</v>
       </c>
       <c r="U16" t="n">
-        <v>0.171</v>
+        <v>0.1045</v>
       </c>
       <c r="V16" t="n">
-        <v>1.7513</v>
+        <v>0.5838</v>
       </c>
       <c r="W16" t="n">
-        <v>1.7513</v>
+        <v>0.5838</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.3083</v>
+        <v>3.1757</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2939</v>
+        <v>1.7581</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0144</v>
+        <v>1.4175</v>
       </c>
       <c r="G17" t="n">
         <v>3.7774</v>
@@ -1780,13 +1780,13 @@
         <v>1.2487</v>
       </c>
       <c r="S17" t="n">
-        <v>0.9232</v>
+        <v>0.7906</v>
       </c>
       <c r="T17" t="n">
-        <v>1.1273</v>
+        <v>0.5915</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2042</v>
+        <v>0.199</v>
       </c>
       <c r="V17" t="n">
         <v>1.5213</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3804</v>
+        <v>1.0463</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1721</v>
+        <v>0.1494</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5525</v>
+        <v>0.897</v>
       </c>
       <c r="G18" t="n">
         <v>-0.0871</v>
@@ -1858,13 +1858,13 @@
         <v>0.2081</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9081</v>
+        <v>-0.2422</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3138</v>
+        <v>0.0076</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5943000000000001</v>
+        <v>-0.2498</v>
       </c>
       <c r="V18" t="n">
         <v>1.1675</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>W. LEVEQUE</t>
+          <t>A. LAFUENTE SISO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3795</v>
+        <v>1.0227</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6851</v>
+        <v>-1.1221</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3056</v>
+        <v>2.1449</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8119</v>
+        <v>2.7273</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.3197</v>
+        <v>1.6782</v>
       </c>
       <c r="I19" t="n">
-        <v>1.1316</v>
+        <v>1.0491</v>
       </c>
       <c r="J19" t="n">
-        <v>0.216</v>
+        <v>2.8868</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.4501</v>
+        <v>2.4133</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6662</v>
+        <v>0.4735</v>
       </c>
       <c r="M19" t="n">
-        <v>0.5958</v>
+        <v>-0.1595</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1304</v>
+        <v>-0.7351</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4654</v>
+        <v>0.5756</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.4162</v>
+        <v>-2.0812</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0406</v>
+        <v>-4.1624</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6244</v>
+        <v>2.0812</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5676</v>
+        <v>0.3766</v>
       </c>
       <c r="T19" t="n">
-        <v>1.0497</v>
+        <v>0.1534</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4821</v>
+        <v>0.2232</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.5838</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.4599</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0437</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. FOREMAN JR</t>
+          <t>W. LEVEQUE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,40 +1969,40 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1506</v>
+        <v>-0.3007</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.6143</v>
+        <v>0.0421</v>
       </c>
       <c r="F20" t="n">
-        <v>0.765</v>
+        <v>-0.3428</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.5928</v>
+        <v>0.8119</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.2515</v>
+        <v>-0.3197</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3413</v>
+        <v>1.1316</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.8904</v>
+        <v>0.216</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.0472</v>
+        <v>-0.4501</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1568</v>
+        <v>0.6662</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.7023</v>
+        <v>0.5958</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2043</v>
+        <v>0.1304</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.498</v>
+        <v>0.4654</v>
       </c>
       <c r="P20" t="n">
         <v>-0.4162</v>
@@ -2014,28 +2014,28 @@
         <v>0.6244</v>
       </c>
       <c r="S20" t="n">
-        <v>1.7621</v>
+        <v>-0.1125</v>
       </c>
       <c r="T20" t="n">
-        <v>0.9192</v>
+        <v>0.4067</v>
       </c>
       <c r="U20" t="n">
-        <v>0.843</v>
+        <v>-0.5193</v>
       </c>
       <c r="V20" t="n">
-        <v>1.3975</v>
+        <v>-0.5838</v>
       </c>
       <c r="W20" t="n">
-        <v>1.3975</v>
+        <v>0.4599</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.0437</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. LAFUENTE SISO</t>
+          <t>D. FOREMAN JR</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4408</v>
+        <v>-0.7565</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0866</v>
+        <v>-1.2573</v>
       </c>
       <c r="F21" t="n">
-        <v>1.6457</v>
+        <v>0.5007</v>
       </c>
       <c r="G21" t="n">
-        <v>2.7273</v>
+        <v>-2.5928</v>
       </c>
       <c r="H21" t="n">
-        <v>1.6782</v>
+        <v>-2.2515</v>
       </c>
       <c r="I21" t="n">
-        <v>1.0491</v>
+        <v>-0.3413</v>
       </c>
       <c r="J21" t="n">
-        <v>2.8868</v>
+        <v>-1.8904</v>
       </c>
       <c r="K21" t="n">
-        <v>2.4133</v>
+        <v>-2.0472</v>
       </c>
       <c r="L21" t="n">
-        <v>0.4735</v>
+        <v>0.1568</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1595</v>
+        <v>-0.7023</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.7351</v>
+        <v>-0.2043</v>
       </c>
       <c r="O21" t="n">
-        <v>0.5756</v>
+        <v>-0.498</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.0812</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q21" t="n">
-        <v>-4.1624</v>
+        <v>-1.0406</v>
       </c>
       <c r="R21" t="n">
-        <v>2.0812</v>
+        <v>0.6244</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0869</v>
+        <v>0.855</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8110000000000001</v>
+        <v>0.2763</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2759</v>
+        <v>0.5787</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.3975</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.3975</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.5089</v>
+        <v>-0.9082</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.366</v>
+        <v>-0.7946</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1429</v>
+        <v>-0.1136</v>
       </c>
       <c r="G22" t="n">
         <v>-1.6771</v>
@@ -2170,13 +2170,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4606</v>
+        <v>0.0613</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1924</v>
+        <v>-0.2362</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2682</v>
+        <v>0.2975</v>
       </c>
       <c r="V22" t="n">
         <v>0.7076</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.9815</v>
+        <v>-1.2696</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.4883</v>
+        <v>-2.9525</v>
       </c>
       <c r="F23" t="n">
-        <v>1.5068</v>
+        <v>1.6829</v>
       </c>
       <c r="G23" t="n">
         <v>-2.7915</v>
@@ -2248,13 +2248,13 @@
         <v>1.2487</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2088</v>
+        <v>0.5032</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.55</v>
+        <v>-0.0142</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3412</v>
+        <v>0.5174</v>
       </c>
       <c r="V23" t="n">
         <v>-0.23</v>
@@ -2281,19 +2281,19 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>18.3596</v>
+        <v>19.7882</v>
       </c>
       <c r="E24" t="n">
-        <v>4.3954</v>
+        <v>4.395500000000002</v>
       </c>
       <c r="F24" t="n">
-        <v>13.9642</v>
+        <v>15.3928</v>
       </c>
       <c r="G24" t="n">
         <v>11.0006</v>
       </c>
       <c r="H24" t="n">
-        <v>4.2447</v>
+        <v>4.244700000000001</v>
       </c>
       <c r="I24" t="n">
         <v>6.755899999999999</v>
@@ -2305,7 +2305,7 @@
         <v>5.349399999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>2.449099999999999</v>
+        <v>2.4491</v>
       </c>
       <c r="M24" t="n">
         <v>3.2023</v>
@@ -2314,7 +2314,7 @@
         <v>-1.1045</v>
       </c>
       <c r="O24" t="n">
-        <v>4.3069</v>
+        <v>4.306900000000001</v>
       </c>
       <c r="P24" t="n">
         <v>-4.1624</v>
@@ -2326,13 +2326,13 @@
         <v>10.406</v>
       </c>
       <c r="S24" t="n">
-        <v>4.0385</v>
+        <v>5.4673</v>
       </c>
       <c r="T24" t="n">
         <v>2.8864</v>
       </c>
       <c r="U24" t="n">
-        <v>1.152</v>
+        <v>2.5808</v>
       </c>
       <c r="V24" t="n">
         <v>7.4827</v>
